--- a/data/gases.xlsx
+++ b/data/gases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LICP\code\data\SNUmodel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LICP\code\CIC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB15919D-F6AC-436D-875E-B800D66B681D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691E1A63-2C73-464F-A759-09E3F5535D33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>idx</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,25 +51,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Mass[kg/mol]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>Lambda</t>
+  </si>
+  <si>
+    <t>Mass [kg/mol]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -377,10 +379,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -388,13 +393,16 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
         <v>5</v>
       </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -402,13 +410,16 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4.4000000000000003E-3</v>
+        <v>4.4010000000000001E-2</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -416,13 +427,16 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2.8E-3</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="D3">
         <v>1.2909999999999999</v>
       </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -430,10 +444,13 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>4.4000000000000003E-3</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="D4">
         <v>1.3</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
